--- a/DemonLordRoguelikeMod/Assets/Data/Excel/excel_mod_items_info_girlwarsspine[Mod道具信息-GirlWarsSpine].xlsx
+++ b/DemonLordRoguelikeMod/Assets/Data/Excel/excel_mod_items_info_girlwarsspine[Mod道具信息-GirlWarsSpine].xlsx
@@ -653,13 +653,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1001_SkeletonData&amp;ui_show_data:0.7532;0,0&amp;ui_show_idle_anim:A</t>
@@ -673,7 +672,6 @@
           <t>少女战争幻化药(GirlWars 1001 Painting_1001_SkeletonData)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>1</t>
@@ -701,13 +699,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1002_SkeletonData&amp;ui_show_data:0.6791;0,0&amp;ui_show_idle_anim:A</t>
@@ -721,7 +718,6 @@
           <t>少女战争幻化药(GirlWars 1002 Painting_1002_SkeletonData)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>1</t>
@@ -749,13 +745,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1003_SkeletonData&amp;ui_show_data:0.48;0,0&amp;ui_show_idle_anim:A</t>
@@ -769,7 +764,6 @@
           <t>少女战争幻化药(GirlWars 1003 Painting_1003_SkeletonData)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>1</t>
@@ -797,13 +791,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1004_SkeletonData&amp;ui_show_data:0.6045;0,0&amp;ui_show_idle_anim:A</t>
@@ -817,7 +810,6 @@
           <t>少女战争幻化药(GirlWars 1004 Painting_1004_SkeletonData)</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>1</t>
@@ -845,13 +837,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1005_SkeletonData&amp;ui_show_data:0.5713;0,0&amp;ui_show_idle_anim:A</t>
@@ -865,7 +856,6 @@
           <t>少女战争幻化药(GirlWars 1005 Painting_1005_SkeletonData)</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>1</t>
@@ -893,13 +883,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1006_SkeletonData&amp;ui_show_data:0.5983;0,0&amp;ui_show_idle_anim:A</t>
@@ -913,7 +902,6 @@
           <t>少女战争幻化药(GirlWars 1006 Painting_1006_SkeletonData)</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>1</t>
@@ -941,13 +929,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1007_SkeletonData&amp;ui_show_data:0.6273;0,0&amp;ui_show_idle_anim:A</t>
@@ -961,7 +948,6 @@
           <t>少女战争幻化药(GirlWars 1007 Painting_1007_SkeletonData)</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>1</t>
@@ -989,13 +975,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1008_SkeletonData&amp;ui_show_data:0.3905;0,0&amp;ui_show_idle_anim:A</t>
@@ -1009,7 +994,6 @@
           <t>少女战争幻化药(GirlWars 1008 Painting_1008_SkeletonData)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>1</t>
@@ -1037,13 +1021,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1009_SkeletonData&amp;ui_show_data:0.5867;0,0&amp;ui_show_idle_anim:A</t>
@@ -1057,7 +1040,6 @@
           <t>少女战争幻化药(GirlWars 1009 Painting_1009_SkeletonData)</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1085,13 +1067,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1016_SkeletonData&amp;ui_show_data:0.5496;0,0&amp;ui_show_idle_anim:A</t>
@@ -1105,7 +1086,6 @@
           <t>少女战争幻化药(GirlWars 1016 Painting_1016_SkeletonData)</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>1</t>
@@ -1133,13 +1113,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>ui_show_res:painting_1017_SkeletonData&amp;ui_show_data:0.7239;0,0&amp;ui_show_idle_anim:A</t>
@@ -1153,7 +1132,6 @@
           <t>少女战争幻化药(GirlWars 1017 painting_1017_SkeletonData)</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>1</t>
@@ -1181,13 +1159,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1018_SkeletonData&amp;ui_show_data:0.189;0,0&amp;ui_show_idle_anim:A</t>
@@ -1201,7 +1178,6 @@
           <t>少女战争幻化药(GirlWars 1018 Painting_1018_SkeletonData)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>1</t>
@@ -1229,13 +1205,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1019_SkeletonData&amp;ui_show_data:0.512;0,0&amp;ui_show_idle_anim:A</t>
@@ -1249,7 +1224,6 @@
           <t>少女战争幻化药(GirlWars 1019 Painting_1019_SkeletonData)</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>1</t>
@@ -1277,13 +1251,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1020_SkeletonData&amp;ui_show_data:0.3801;0,0&amp;ui_show_idle_anim:A</t>
@@ -1297,7 +1270,6 @@
           <t>少女战争幻化药(GirlWars 1020 Painting_1020_SkeletonData)</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>1</t>
@@ -1325,13 +1297,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1021_SkeletonData&amp;ui_show_data:0.2796;0,0&amp;ui_show_idle_anim:A</t>
@@ -1345,7 +1316,6 @@
           <t>少女战争幻化药(GirlWars 1021 Painting_1021_SkeletonData)</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>1</t>
@@ -1373,13 +1343,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1023_SkeletonData&amp;ui_show_data:0.2878;0,0&amp;ui_show_idle_anim:A</t>
@@ -1393,7 +1362,6 @@
           <t>少女战争幻化药(GirlWars 1023 Painting_1023_SkeletonData)</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>1</t>
@@ -1421,13 +1389,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1024_SkeletonData&amp;ui_show_data:0.4588;0,0&amp;ui_show_idle_anim:A</t>
@@ -1441,7 +1408,6 @@
           <t>少女战争幻化药(GirlWars 1024 Painting_1024_SkeletonData)</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>1</t>
@@ -1469,13 +1435,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1025_SkeletonData&amp;ui_show_data:0.4856;0,0&amp;ui_show_idle_anim:A</t>
@@ -1489,7 +1454,6 @@
           <t>少女战争幻化药(GirlWars 1025 Painting_1025_SkeletonData)</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>1</t>
@@ -1517,13 +1481,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1026_SkeletonData&amp;ui_show_data:0.6434;0,0&amp;ui_show_idle_anim:A</t>
@@ -1537,7 +1500,6 @@
           <t>少女战争幻化药(GirlWars 1026 Painting_1026_SkeletonData)</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>1</t>
@@ -1565,13 +1527,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1027_SkeletonData&amp;ui_show_data:0.3712;0,0&amp;ui_show_idle_anim:A</t>
@@ -1585,7 +1546,6 @@
           <t>少女战争幻化药(GirlWars 1027 Painting_1027_SkeletonData)</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>1</t>
@@ -1613,13 +1573,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1028_SkeletonData&amp;ui_show_data:0.5425;0,0&amp;ui_show_idle_anim:A</t>
@@ -1633,7 +1592,6 @@
           <t>少女战争幻化药(GirlWars 1028 Painting_1028_SkeletonData)</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>1</t>
@@ -1661,13 +1619,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1029_SkeletonData&amp;ui_show_data:0.5297;0,0&amp;ui_show_idle_anim:A</t>
@@ -1681,7 +1638,6 @@
           <t>少女战争幻化药(GirlWars 1029 Painting_1029_SkeletonData)</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>1</t>
@@ -1709,13 +1665,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1030_SkeletonData&amp;ui_show_data:0.6345;0,0&amp;ui_show_idle_anim:A</t>
@@ -1729,7 +1684,6 @@
           <t>少女战争幻化药(GirlWars 1030 Painting_1030_SkeletonData)</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>1</t>
@@ -1757,13 +1711,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1031_SkeletonData&amp;ui_show_data:0.7191;0,0&amp;ui_show_idle_anim:A</t>
@@ -1777,7 +1730,6 @@
           <t>少女战争幻化药(GirlWars 1031 Painting_1031_SkeletonData)</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>1</t>
@@ -1805,13 +1757,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1032_SkeletonData&amp;ui_show_data:0.3225;0,0&amp;ui_show_idle_anim:A</t>
@@ -1825,7 +1776,6 @@
           <t>少女战争幻化药(GirlWars 1032 Painting_1032_SkeletonData)</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>1</t>
@@ -1853,13 +1803,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1033_SkeletonData&amp;ui_show_data:0.5417;0,0&amp;ui_show_idle_anim:A</t>
@@ -1873,7 +1822,6 @@
           <t>少女战争幻化药(GirlWars 1033 Painting_1033_SkeletonData)</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>1</t>
@@ -1901,13 +1849,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1034_SkeletonData&amp;ui_show_data:0.4024;0,0&amp;ui_show_idle_anim:A</t>
@@ -1921,7 +1868,6 @@
           <t>少女战争幻化药(GirlWars 1034 Painting_1034_SkeletonData)</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>1</t>
@@ -1949,13 +1895,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1035_SkeletonData&amp;ui_show_data:0.4823;0,0&amp;ui_show_idle_anim:A</t>
@@ -1969,7 +1914,6 @@
           <t>少女战争幻化药(GirlWars 1035 Painting_1035_SkeletonData)</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>1</t>
@@ -1997,13 +1941,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1036_SkeletonData&amp;ui_show_data:0.5089;0,0&amp;ui_show_idle_anim:A</t>
@@ -2017,7 +1960,6 @@
           <t>少女战争幻化药(GirlWars 1036 Painting_1036_SkeletonData)</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>1</t>
@@ -2045,13 +1987,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>ui_show_res:painting_1038_SkeletonData&amp;ui_show_data:0.5444;0,0&amp;ui_show_idle_anim:A</t>
@@ -2065,7 +2006,6 @@
           <t>少女战争幻化药(GirlWars 1038 painting_1038_SkeletonData)</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>1</t>
@@ -2093,13 +2033,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>ui_show_res:painting_1039_SkeletonData&amp;ui_show_data:0.3647;0,0&amp;ui_show_idle_anim:A</t>
@@ -2113,7 +2052,6 @@
           <t>少女战争幻化药(GirlWars 1039 painting_1039_SkeletonData)</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>1</t>
@@ -2141,13 +2079,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>ui_show_res:painting_1040_SkeletonData&amp;ui_show_data:0.3346;0,0&amp;ui_show_idle_anim:A</t>
@@ -2161,7 +2098,6 @@
           <t>少女战争幻化药(GirlWars 1040 painting_1040_SkeletonData)</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>1</t>
@@ -2189,13 +2125,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1041_SkeletonData&amp;ui_show_data:0.3995;0,0&amp;ui_show_idle_anim:A</t>
@@ -2209,7 +2144,6 @@
           <t>少女战争幻化药(GirlWars 1041 Painting_1041_SkeletonData)</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>1</t>
@@ -2237,13 +2171,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1042_SkeletonData&amp;ui_show_data:0.2638;0,0&amp;ui_show_idle_anim:A</t>
@@ -2257,7 +2190,6 @@
           <t>少女战争幻化药(GirlWars 1042 Painting_1042_SkeletonData)</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>1</t>
@@ -2285,13 +2217,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>ui_show_res:painting_1043_SkeletonData&amp;ui_show_data:0.4772;0,0&amp;ui_show_idle_anim:A</t>
@@ -2305,7 +2236,6 @@
           <t>少女战争幻化药(GirlWars 1043 painting_1043_SkeletonData)</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>1</t>
@@ -2333,13 +2263,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1044_SkeletonData&amp;ui_show_data:0.5932;0,0&amp;ui_show_idle_anim:A</t>
@@ -2353,7 +2282,6 @@
           <t>少女战争幻化药(GirlWars 1044 Painting_1044_SkeletonData)</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>1</t>
@@ -2381,13 +2309,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>ui_show_res:painting_1045_SkeletonData&amp;ui_show_data:0.6628;0,0&amp;ui_show_idle_anim:A</t>
@@ -2401,7 +2328,6 @@
           <t>少女战争幻化药(GirlWars 1045 painting_1045_SkeletonData)</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>1</t>
@@ -2429,13 +2355,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>ui_show_res:painting_1046_SkeletonData&amp;ui_show_data:0.5042;0,0&amp;ui_show_idle_anim:A</t>
@@ -2449,7 +2374,6 @@
           <t>少女战争幻化药(GirlWars 1046 painting_1046_SkeletonData)</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>1</t>
@@ -2477,13 +2401,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>ui_show_res:painting_1047_SkeletonData&amp;ui_show_data:0.8149;0,0&amp;ui_show_idle_anim:A</t>
@@ -2497,7 +2420,6 @@
           <t>少女战争幻化药(GirlWars 1047 painting_1047_SkeletonData)</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>1</t>
@@ -2525,13 +2447,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1048_SkeletonData&amp;ui_show_data:0.5108;0,0&amp;ui_show_idle_anim:A</t>
@@ -2545,7 +2466,6 @@
           <t>少女战争幻化药(GirlWars 1048 Painting_1048_SkeletonData)</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>1</t>
@@ -2573,13 +2493,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1049_SkeletonData&amp;ui_show_data:0.5748;0,0&amp;ui_show_idle_anim:A</t>
@@ -2593,7 +2512,6 @@
           <t>少女战争幻化药(GirlWars 1049 Painting_1049_SkeletonData)</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>1</t>
@@ -2621,13 +2539,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1050_SkeletonData&amp;ui_show_data:0.6423;0,0&amp;ui_show_idle_anim:A</t>
@@ -2641,7 +2558,6 @@
           <t>少女战争幻化药(GirlWars 1050 Painting_1050_SkeletonData)</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>1</t>
@@ -2669,13 +2585,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>ui_show_res:painting_1051_SkeletonData&amp;ui_show_data:0.5808;0,0&amp;ui_show_idle_anim:A</t>
@@ -2689,7 +2604,6 @@
           <t>少女战争幻化药(GirlWars 1051 painting_1051_SkeletonData)</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>1</t>
@@ -2717,13 +2631,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1052_SkeletonData&amp;ui_show_data:0.5724;0,0&amp;ui_show_idle_anim:A</t>
@@ -2737,7 +2650,6 @@
           <t>少女战争幻化药(GirlWars 1052 Painting_1052_SkeletonData)</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>1</t>
@@ -2765,13 +2677,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1053_SkeletonData&amp;ui_show_data:0.4476;0,0&amp;ui_show_idle_anim:A</t>
@@ -2785,7 +2696,6 @@
           <t>少女战争幻化药(GirlWars 1053 Painting_1053_SkeletonData)</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>1</t>
@@ -2813,13 +2723,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1055_SkeletonData&amp;ui_show_data:0.4269;0,0&amp;ui_show_idle_anim:A</t>
@@ -2833,7 +2742,6 @@
           <t>少女战争幻化药(GirlWars 1055 Painting_1055_SkeletonData)</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>1</t>
@@ -2861,13 +2769,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>ui_show_res:painting_1056_SkeletonData&amp;ui_show_data:0.4013;0,0&amp;ui_show_idle_anim:A</t>
@@ -2881,7 +2788,6 @@
           <t>少女战争幻化药(GirlWars 1056 painting_1056_SkeletonData)</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>1</t>
@@ -2909,13 +2815,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1057_SkeletonData&amp;ui_show_data:0.5155;0,0&amp;ui_show_idle_anim:A</t>
@@ -2929,7 +2834,6 @@
           <t>少女战争幻化药(GirlWars 1057 Painting_1057_SkeletonData)</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>1</t>
@@ -2957,13 +2861,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1058_SkeletonData&amp;ui_show_data:0.3989;0,0&amp;ui_show_idle_anim:A</t>
@@ -2977,7 +2880,6 @@
           <t>少女战争幻化药(GirlWars 1058 Painting_1058_SkeletonData)</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>1</t>
@@ -3005,13 +2907,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1059_SkeletonData&amp;ui_show_data:0.4312;0,0&amp;ui_show_idle_anim:A</t>
@@ -3025,7 +2926,6 @@
           <t>少女战争幻化药(GirlWars 1059 Painting_1059_SkeletonData)</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>1</t>
@@ -3053,13 +2953,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1060_SkeletonData&amp;ui_show_data:0.557;0,0&amp;ui_show_idle_anim:A</t>
@@ -3073,7 +2972,6 @@
           <t>少女战争幻化药(GirlWars 1060 Painting_1060_SkeletonData)</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>1</t>
@@ -3101,13 +2999,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1061_SkeletonData&amp;ui_show_data:0.6424;0,0&amp;ui_show_idle_anim:A</t>
@@ -3121,7 +3018,6 @@
           <t>少女战争幻化药(GirlWars 1061 Painting_1061_SkeletonData)</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>1</t>
@@ -3149,13 +3045,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1062_SkeletonData&amp;ui_show_data:0.365;0,0&amp;ui_show_idle_anim:A</t>
@@ -3169,7 +3064,6 @@
           <t>少女战争幻化药(GirlWars 1062 Painting_1062_SkeletonData)</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>1</t>
@@ -3197,13 +3091,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1063_SkeletonData&amp;ui_show_data:0.7192;0,0&amp;ui_show_idle_anim:A</t>
@@ -3217,7 +3110,6 @@
           <t>少女战争幻化药(GirlWars 1063 Painting_1063_SkeletonData)</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>1</t>
@@ -3245,13 +3137,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1064_SkeletonData&amp;ui_show_data:0.5778;0,0&amp;ui_show_idle_anim:A</t>
@@ -3265,7 +3156,6 @@
           <t>少女战争幻化药(GirlWars 1064 Painting_1064_SkeletonData)</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>1</t>
@@ -3293,13 +3183,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1065_SkeletonData&amp;ui_show_data:0.543;0,0&amp;ui_show_idle_anim:A</t>
@@ -3313,7 +3202,6 @@
           <t>少女战争幻化药(GirlWars 1065 Painting_1065_SkeletonData)</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>1</t>
@@ -3341,13 +3229,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1066_SkeletonData&amp;ui_show_data:0.6164;0,0&amp;ui_show_idle_anim:A</t>
@@ -3361,7 +3248,6 @@
           <t>少女战争幻化药(GirlWars 1066 Painting_1066_SkeletonData)</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>1</t>
@@ -3389,13 +3275,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1067_SkeletonData&amp;ui_show_data:0.5254;0,0&amp;ui_show_idle_anim:A</t>
@@ -3409,7 +3294,6 @@
           <t>少女战争幻化药(GirlWars 1067 Painting_1067_SkeletonData)</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>1</t>
@@ -3437,13 +3321,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1068_SkeletonData&amp;ui_show_data:0.6079;0,0&amp;ui_show_idle_anim:A</t>
@@ -3457,7 +3340,6 @@
           <t>少女战争幻化药(GirlWars 1068 Painting_1068_SkeletonData)</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>1</t>
@@ -3485,13 +3367,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1098_SkeletonData&amp;ui_show_data:0.6513;0,0&amp;ui_show_idle_anim:A</t>
@@ -3505,7 +3386,6 @@
           <t>少女战争幻化药(GirlWars 1098 Painting_1098_SkeletonData)</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>1</t>
@@ -3533,13 +3413,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_1099_SkeletonData&amp;ui_show_data:0.5236;0,0&amp;ui_show_idle_anim:A</t>
@@ -3553,7 +3432,6 @@
           <t>少女战争幻化药(GirlWars 1099 Painting_1099_SkeletonData)</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>1</t>
@@ -3581,13 +3459,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21012_SkeletonData&amp;ui_show_data:0.5719;0,0&amp;ui_show_idle_anim:A</t>
@@ -3601,7 +3478,6 @@
           <t>少女战争幻化药(GirlWars 21012 Painting_21012_SkeletonData)</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>1</t>
@@ -3629,13 +3505,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21015_SkeletonData&amp;ui_show_data:0.5059;0,0&amp;ui_show_idle_anim:A</t>
@@ -3649,7 +3524,6 @@
           <t>少女战争幻化药(GirlWars 21015 Painting_21015_SkeletonData)</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>1</t>
@@ -3677,13 +3551,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21025_SkeletonData&amp;ui_show_data:0.59;0,0&amp;ui_show_idle_anim:A</t>
@@ -3697,7 +3570,6 @@
           <t>少女战争幻化药(GirlWars 21025 Painting_21025_SkeletonData)</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>1</t>
@@ -3725,13 +3597,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21029_SkeletonData&amp;ui_show_data:0.5393;0,0&amp;ui_show_idle_anim:A</t>
@@ -3745,7 +3616,6 @@
           <t>少女战争幻化药(GirlWars 21029 Painting_21029_SkeletonData)</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>1</t>
@@ -3773,13 +3643,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21039_SkeletonData&amp;ui_show_data:0.7045;0,0&amp;ui_show_idle_anim:A</t>
@@ -3793,7 +3662,6 @@
           <t>少女战争幻化药(GirlWars 21039 Painting_21039_SkeletonData)</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>1</t>
@@ -3821,13 +3689,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21041_SkeletonData&amp;ui_show_data:0.4743;0,0&amp;ui_show_idle_anim:A</t>
@@ -3841,7 +3708,6 @@
           <t>少女战争幻化药(GirlWars 21041 Painting_21041_SkeletonData)</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>1</t>
@@ -3869,13 +3735,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21043_SkeletonData&amp;ui_show_data:0.5762;0,0&amp;ui_show_idle_anim:A</t>
@@ -3889,7 +3754,6 @@
           <t>少女战争幻化药(GirlWars 21043 Painting_21043_SkeletonData)</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>1</t>
@@ -3917,13 +3781,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>ui_show_res:painting_21044_SkeletonData&amp;ui_show_data:0.1311;0,0&amp;ui_show_idle_anim:A</t>
@@ -3937,7 +3800,6 @@
           <t>少女战争幻化药(GirlWars 21044 painting_21044_SkeletonData)</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>1</t>
@@ -3965,13 +3827,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21048_SkeletonData&amp;ui_show_data:0.7018;0,0&amp;ui_show_idle_anim:A</t>
@@ -3985,7 +3846,6 @@
           <t>少女战争幻化药(GirlWars 21048 Painting_21048_SkeletonData)</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>1</t>
@@ -4013,13 +3873,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21049_SkeletonData&amp;ui_show_data:0.6221;0,0&amp;ui_show_idle_anim:A</t>
@@ -4033,7 +3892,6 @@
           <t>少女战争幻化药(GirlWars 21049 Painting_21049_SkeletonData)</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>1</t>
@@ -4061,13 +3919,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21058_SkeletonData&amp;ui_show_data:0.6064;0,0&amp;ui_show_idle_anim:A</t>
@@ -4081,7 +3938,6 @@
           <t>少女战争幻化药(GirlWars 21058 Painting_21058_SkeletonData)</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>1</t>
@@ -4109,13 +3965,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21070_SkeletonData&amp;ui_show_data:0.4326;0,0&amp;ui_show_idle_anim:A</t>
@@ -4129,7 +3984,6 @@
           <t>少女战争幻化药(GirlWars 21070 Painting_21070_SkeletonData)</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>1</t>
@@ -4157,13 +4011,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>ui_show_res:painting_21072_SkeletonData&amp;ui_show_data:0.689;0,0&amp;ui_show_idle_anim:A</t>
@@ -4177,7 +4030,6 @@
           <t>少女战争幻化药(GirlWars 21072 painting_21072_SkeletonData)</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>1</t>
@@ -4205,13 +4057,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21073_SkeletonData&amp;ui_show_data:0.4151;0,0&amp;ui_show_idle_anim:A</t>
@@ -4225,7 +4076,6 @@
           <t>少女战争幻化药(GirlWars 21073 Painting_21073_SkeletonData)</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>1</t>
@@ -4253,13 +4103,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21074_SkeletonData&amp;ui_show_data:0.307;0,0&amp;ui_show_idle_anim:A</t>
@@ -4273,7 +4122,6 @@
           <t>少女战争幻化药(GirlWars 21074 Painting_21074_SkeletonData)</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>1</t>
@@ -4301,13 +4149,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21075_SkeletonData&amp;ui_show_data:0.9414;0,0&amp;ui_show_idle_anim:A</t>
@@ -4321,7 +4168,6 @@
           <t>少女战争幻化药(GirlWars 21075 Painting_21075_SkeletonData)</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>1</t>
@@ -4349,13 +4195,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21076_SkeletonData&amp;ui_show_data:0.7968;0,0&amp;ui_show_idle_anim:A</t>
@@ -4369,7 +4214,6 @@
           <t>少女战争幻化药(GirlWars 21076 Painting_21076_SkeletonData)</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>1</t>
@@ -4397,13 +4241,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>ui_show_res:painting_21077_SkeletonData&amp;ui_show_data:0.4757;0,0&amp;ui_show_idle_anim:A</t>
@@ -4417,7 +4260,6 @@
           <t>少女战争幻化药(GirlWars 21077 painting_21077_SkeletonData)</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>1</t>
@@ -4445,13 +4287,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21078_SkeletonData&amp;ui_show_data:0.3901;0,0&amp;ui_show_idle_anim:A</t>
@@ -4465,7 +4306,6 @@
           <t>少女战争幻化药(GirlWars 21078 Painting_21078_SkeletonData)</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>1</t>
@@ -4493,13 +4333,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21079_SkeletonData&amp;ui_show_data:0.5355;0,0&amp;ui_show_idle_anim:A</t>
@@ -4513,7 +4352,6 @@
           <t>少女战争幻化药(GirlWars 21079 Painting_21079_SkeletonData)</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>1</t>
@@ -4541,13 +4379,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21080_SkeletonData&amp;ui_show_data:0.7066;0,0&amp;ui_show_idle_anim:A</t>
@@ -4561,7 +4398,6 @@
           <t>少女战争幻化药(GirlWars 21080 Painting_21080_SkeletonData)</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>1</t>
@@ -4589,13 +4425,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21081_SkeletonData&amp;ui_show_data:0.6602;0,0&amp;ui_show_idle_anim:A</t>
@@ -4609,7 +4444,6 @@
           <t>少女战争幻化药(GirlWars 21081 Painting_21081_SkeletonData)</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>1</t>
@@ -4637,13 +4471,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21082_SkeletonData&amp;ui_show_data:0.7107;0,0&amp;ui_show_idle_anim:A</t>
@@ -4657,7 +4490,6 @@
           <t>少女战争幻化药(GirlWars 21082 Painting_21082_SkeletonData)</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>1</t>
@@ -4685,13 +4517,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21083_SkeletonData&amp;ui_show_data:0.6602;0,0&amp;ui_show_idle_anim:A</t>
@@ -4705,7 +4536,6 @@
           <t>少女战争幻化药(GirlWars 21083 Painting_21083_SkeletonData)</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>1</t>
@@ -4733,13 +4563,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21084_SkeletonData&amp;ui_show_data:0.495;0,0&amp;ui_show_idle_anim:A</t>
@@ -4753,7 +4582,6 @@
           <t>少女战争幻化药(GirlWars 21084 Painting_21084_SkeletonData)</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>1</t>
@@ -4781,13 +4609,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21085_SkeletonData&amp;ui_show_data:0.5376;0,0&amp;ui_show_idle_anim:A</t>
@@ -4801,7 +4628,6 @@
           <t>少女战争幻化药(GirlWars 21085 Painting_21085_SkeletonData)</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>1</t>
@@ -4829,13 +4655,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21086_SkeletonData&amp;ui_show_data:0.5236;0,0&amp;ui_show_idle_anim:A</t>
@@ -4849,7 +4674,6 @@
           <t>少女战争幻化药(GirlWars 21086 Painting_21086_SkeletonData)</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>1</t>
@@ -4877,13 +4701,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21087_SkeletonData&amp;ui_show_data:0.6119;0,0&amp;ui_show_idle_anim:A</t>
@@ -4897,7 +4720,6 @@
           <t>少女战争幻化药(GirlWars 21087 Painting_21087_SkeletonData)</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>1</t>
@@ -4925,13 +4747,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21088_SkeletonData&amp;ui_show_data:0.6593;0,0&amp;ui_show_idle_anim:A</t>
@@ -4945,7 +4766,6 @@
           <t>少女战争幻化药(GirlWars 21088 Painting_21088_SkeletonData)</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>1</t>
@@ -4973,13 +4793,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21089_SkeletonData&amp;ui_show_data:0.5511;0,0&amp;ui_show_idle_anim:A</t>
@@ -4993,7 +4812,6 @@
           <t>少女战争幻化药(GirlWars 21089 Painting_21089_SkeletonData)</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>1</t>
@@ -5021,13 +4839,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21090_SkeletonData&amp;ui_show_data:0.4875;0,0&amp;ui_show_idle_anim:A</t>
@@ -5041,7 +4858,6 @@
           <t>少女战争幻化药(GirlWars 21090 Painting_21090_SkeletonData)</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>1</t>
@@ -5069,13 +4885,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21101_SkeletonData&amp;ui_show_data:0.6258;0,0&amp;ui_show_idle_anim:A</t>
@@ -5089,7 +4904,6 @@
           <t>少女战争幻化药(GirlWars 21101 Painting_21101_SkeletonData)</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>1</t>
@@ -5117,13 +4931,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_21104_SkeletonData&amp;ui_show_data:0.5354;0,0&amp;ui_show_idle_anim:A</t>
@@ -5137,7 +4950,6 @@
           <t>少女战争幻化药(GirlWars 21104 Painting_21104_SkeletonData)</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>1</t>
@@ -5165,13 +4977,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H98" t="n">
         <v>0</v>
       </c>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31012_SkeletonData&amp;ui_show_data:0.5299;0,0&amp;ui_show_idle_anim:A</t>
@@ -5185,7 +4996,6 @@
           <t>少女战争幻化药(GirlWars 31012 Painting_31012_SkeletonData)</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>1</t>
@@ -5213,13 +5023,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31015_SkeletonData&amp;ui_show_data:0.5641;0,0&amp;ui_show_idle_anim:A</t>
@@ -5233,7 +5042,6 @@
           <t>少女战争幻化药(GirlWars 31015 Painting_31015_SkeletonData)</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>1</t>
@@ -5261,13 +5069,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31025_SkeletonData&amp;ui_show_data:0.4606;0,0&amp;ui_show_idle_anim:A</t>
@@ -5281,7 +5088,6 @@
           <t>少女战争幻化药(GirlWars 31025 Painting_31025_SkeletonData)</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
           <t>1</t>
@@ -5309,13 +5115,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31041_SkeletonData&amp;ui_show_data:0.5744;0,0&amp;ui_show_idle_anim:A</t>
@@ -5329,7 +5134,6 @@
           <t>少女战争幻化药(GirlWars 31041 Painting_31041_SkeletonData)</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
           <t>1</t>
@@ -5357,13 +5161,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H102" t="n">
         <v>0</v>
       </c>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31044_SkeletonData&amp;ui_show_data:0.3825;0,0&amp;ui_show_idle_anim:A</t>
@@ -5377,7 +5180,6 @@
           <t>少女战争幻化药(GirlWars 31044 Painting_31044_SkeletonData)</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
           <t>1</t>
@@ -5405,13 +5207,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31070_SkeletonData&amp;ui_show_data:0.6754;0,0&amp;ui_show_idle_anim:A</t>
@@ -5425,7 +5226,6 @@
           <t>少女战争幻化药(GirlWars 31070 Painting_31070_SkeletonData)</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
           <t>1</t>
@@ -5453,13 +5253,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31072_SkeletonData&amp;ui_show_data:0.583;0,0&amp;ui_show_idle_anim:A</t>
@@ -5473,7 +5272,6 @@
           <t>少女战争幻化药(GirlWars 31072 Painting_31072_SkeletonData)</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
           <t>1</t>
@@ -5501,13 +5299,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31073_SkeletonData&amp;ui_show_data:0.5748;0,0&amp;ui_show_idle_anim:A</t>
@@ -5521,7 +5318,6 @@
           <t>少女战争幻化药(GirlWars 31073 Painting_31073_SkeletonData)</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
           <t>1</t>
@@ -5549,13 +5345,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H106" t="n">
         <v>0</v>
       </c>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31079_SkeletonData&amp;ui_show_data:0.4929;0,0&amp;ui_show_idle_anim:A</t>
@@ -5569,7 +5364,6 @@
           <t>少女战争幻化药(GirlWars 31079 Painting_31079_SkeletonData)</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
           <t>1</t>
@@ -5597,13 +5391,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H107" t="n">
         <v>0</v>
       </c>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31103_SkeletonData&amp;ui_show_data:0.5559;0,0&amp;ui_show_idle_anim:A</t>
@@ -5617,7 +5410,6 @@
           <t>少女战争幻化药(GirlWars 31103 Painting_31103_SkeletonData)</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
           <t>1</t>
@@ -5645,13 +5437,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31105_SkeletonData&amp;ui_show_data:0.7423;0,0&amp;ui_show_idle_anim:A</t>
@@ -5665,7 +5456,6 @@
           <t>少女战争幻化药(GirlWars 31105 Painting_31105_SkeletonData)</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
           <t>1</t>
@@ -5693,13 +5483,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31106_SkeletonData&amp;ui_show_data:0.6173;0,0&amp;ui_show_idle_anim:A</t>
@@ -5713,7 +5502,6 @@
           <t>少女战争幻化药(GirlWars 31106 Painting_31106_SkeletonData)</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
           <t>1</t>
@@ -5741,13 +5529,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31107_SkeletonData&amp;ui_show_data:0.6006;0,0&amp;ui_show_idle_anim:A</t>
@@ -5761,7 +5548,6 @@
           <t>少女战争幻化药(GirlWars 31107 Painting_31107_SkeletonData)</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
           <t>1</t>
@@ -5789,13 +5575,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31108_SkeletonData&amp;ui_show_data:0.4489;0,0&amp;ui_show_idle_anim:A</t>
@@ -5809,7 +5594,6 @@
           <t>少女战争幻化药(GirlWars 31108 Painting_31108_SkeletonData)</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
           <t>1</t>
@@ -5837,13 +5621,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31109_SkeletonData&amp;ui_show_data:0.5882;0,0&amp;ui_show_idle_anim:A</t>
@@ -5857,7 +5640,6 @@
           <t>少女战争幻化药(GirlWars 31109 Painting_31109_SkeletonData)</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
           <t>1</t>
@@ -5885,13 +5667,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31110_SkeletonData&amp;ui_show_data:0.6342;0,0&amp;ui_show_idle_anim:A</t>
@@ -5905,7 +5686,6 @@
           <t>少女战争幻化药(GirlWars 31110 Painting_31110_SkeletonData)</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
           <t>1</t>
@@ -5933,13 +5713,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H114" t="n">
         <v>0</v>
       </c>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31111_SkeletonData&amp;ui_show_data:0.4803;0,0&amp;ui_show_idle_anim:A</t>
@@ -5953,7 +5732,6 @@
           <t>少女战争幻化药(GirlWars 31111 Painting_31111_SkeletonData)</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
           <t>1</t>
@@ -5981,13 +5759,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31112_SkeletonData&amp;ui_show_data:0.5639;0,0&amp;ui_show_idle_anim:A</t>
@@ -6001,7 +5778,6 @@
           <t>少女战争幻化药(GirlWars 31112 Painting_31112_SkeletonData)</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
           <t>1</t>
@@ -6029,13 +5805,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31113_SkeletonData&amp;ui_show_data:0.5019;0,0&amp;ui_show_idle_anim:A</t>
@@ -6049,7 +5824,6 @@
           <t>少女战争幻化药(GirlWars 31113 Painting_31113_SkeletonData)</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
           <t>1</t>
@@ -6077,13 +5851,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H117" t="n">
         <v>0</v>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31114_SkeletonData&amp;ui_show_data:0.5744;0,0&amp;ui_show_idle_anim:A</t>
@@ -6097,7 +5870,6 @@
           <t>少女战争幻化药(GirlWars 31114 Painting_31114_SkeletonData)</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
           <t>1</t>
@@ -6125,13 +5897,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31115_SkeletonData&amp;ui_show_data:0.3663;0,0&amp;ui_show_idle_anim:A</t>
@@ -6145,7 +5916,6 @@
           <t>少女战争幻化药(GirlWars 31115 Painting_31115_SkeletonData)</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
           <t>1</t>
@@ -6173,13 +5943,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H119" t="n">
         <v>0</v>
       </c>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31116_SkeletonData&amp;ui_show_data:0.3381;0,0&amp;ui_show_idle_anim:A</t>
@@ -6193,7 +5962,6 @@
           <t>少女战争幻化药(GirlWars 31116 Painting_31116_SkeletonData)</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
           <t>1</t>
@@ -6221,13 +5989,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H120" t="n">
         <v>0</v>
       </c>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31117_SkeletonData&amp;ui_show_data:0.3893;0,0&amp;ui_show_idle_anim:A</t>
@@ -6241,7 +6008,6 @@
           <t>少女战争幻化药(GirlWars 31117 Painting_31117_SkeletonData)</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
           <t>1</t>
@@ -6269,13 +6035,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H121" t="n">
         <v>0</v>
       </c>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31118_SkeletonData&amp;ui_show_data:0.2714;0,0&amp;ui_show_idle_anim:A</t>
@@ -6289,7 +6054,6 @@
           <t>少女战争幻化药(GirlWars 31118 Painting_31118_SkeletonData)</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
           <t>1</t>
@@ -6317,13 +6081,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31119_SkeletonData&amp;ui_show_data:0.4456;0,0&amp;ui_show_idle_anim:A</t>
@@ -6337,7 +6100,6 @@
           <t>少女战争幻化药(GirlWars 31119 Painting_31119_SkeletonData)</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
           <t>1</t>
@@ -6365,13 +6127,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_31120_SkeletonData&amp;ui_show_data:0.4715;0,0&amp;ui_show_idle_anim:A</t>
@@ -6385,7 +6146,6 @@
           <t>少女战争幻化药(GirlWars 31120 Painting_31120_SkeletonData)</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
           <t>1</t>
@@ -6413,13 +6173,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H124" t="n">
         <v>0</v>
       </c>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_80001_SkeletonData&amp;ui_show_data:0.7869;0,0&amp;ui_show_idle_anim:A</t>
@@ -6433,7 +6192,6 @@
           <t>少女战争幻化药(GirlWars 80001 Painting_80001_SkeletonData)</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
           <t>1</t>
@@ -6461,13 +6219,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H125" t="n">
         <v>0</v>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_81001_SkeletonData&amp;ui_show_data:1.438;0,0&amp;ui_show_idle_anim:A</t>
@@ -6481,7 +6238,6 @@
           <t>少女战争幻化药(GirlWars 81001 Painting_81001_SkeletonData)</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
           <t>1</t>
@@ -6509,13 +6265,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_81002_SkeletonData&amp;ui_show_data:0.8892;0,0&amp;ui_show_idle_anim:A</t>
@@ -6529,7 +6284,6 @@
           <t>少女战争幻化药(GirlWars 81002 Painting_81002_SkeletonData)</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
           <t>1</t>
@@ -6557,13 +6311,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H127" t="n">
         <v>0</v>
       </c>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_81003_SkeletonData&amp;ui_show_data:1.6;0,0&amp;ui_show_idle_anim:A</t>
@@ -6577,7 +6330,6 @@
           <t>少女战争幻化药(GirlWars 81003 Painting_81003_SkeletonData)</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
           <t>1</t>
@@ -6605,13 +6357,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_81004_SkeletonData&amp;ui_show_data:0.6629;0,0&amp;ui_show_idle_anim:A</t>
@@ -6625,7 +6376,6 @@
           <t>少女战争幻化药(GirlWars 81004 Painting_81004_SkeletonData)</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
           <t>1</t>
@@ -6653,13 +6403,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_81005_SkeletonData&amp;ui_show_data:1.2106;0,0&amp;ui_show_idle_anim:A</t>
@@ -6673,7 +6422,6 @@
           <t>少女战争幻化药(GirlWars 81005 Painting_81005_SkeletonData)</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
           <t>1</t>
@@ -6701,13 +6449,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_81008_SkeletonData&amp;ui_show_data:1.2132;0,0&amp;ui_show_idle_anim:A</t>
@@ -6721,7 +6468,6 @@
           <t>少女战争幻化药(GirlWars 81008 Painting_81008_SkeletonData)</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
           <t>1</t>
@@ -6749,13 +6495,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_81009_SkeletonData&amp;ui_show_data:1.1873;0,0&amp;ui_show_idle_anim:A</t>
@@ -6769,7 +6514,6 @@
           <t>少女战争幻化药(GirlWars 81009 Painting_81009_SkeletonData)</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
           <t>1</t>
@@ -6797,13 +6541,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H132" t="n">
         <v>0</v>
       </c>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_81010_SkeletonData&amp;ui_show_data:0.8144;0,0&amp;ui_show_idle_anim:A</t>
@@ -6817,7 +6560,6 @@
           <t>少女战争幻化药(GirlWars 81010 Painting_81010_SkeletonData)</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
           <t>1</t>
@@ -6845,13 +6587,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_81011_SkeletonData&amp;ui_show_data:1.2098;0,0&amp;ui_show_idle_anim:A</t>
@@ -6865,7 +6606,6 @@
           <t>少女战争幻化药(GirlWars 81011 Painting_81011_SkeletonData)</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
           <t>1</t>
@@ -6893,13 +6633,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_81012_SkeletonData&amp;ui_show_data:0.9436;0,0&amp;ui_show_idle_anim:A</t>
@@ -6913,7 +6652,6 @@
           <t>少女战争幻化药(GirlWars 81012 Painting_81012_SkeletonData)</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
           <t>1</t>
@@ -6941,13 +6679,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H135" t="n">
         <v>0</v>
       </c>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_82001_SkeletonData&amp;ui_show_data:1.0087;0,0&amp;ui_show_idle_anim:A</t>
@@ -6961,7 +6698,6 @@
           <t>少女战争幻化药(GirlWars 82001 Painting_82001_SkeletonData)</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
           <t>1</t>
@@ -6989,13 +6725,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H136" t="n">
         <v>0</v>
       </c>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_82002_SkeletonData&amp;ui_show_data:0.5769;0,0&amp;ui_show_idle_anim:A</t>
@@ -7009,7 +6744,6 @@
           <t>少女战争幻化药(GirlWars 82002 Painting_82002_SkeletonData)</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
           <t>1</t>
@@ -7037,13 +6771,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H137" t="n">
         <v>0</v>
       </c>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_82003_SkeletonData&amp;ui_show_data:1.1099;0,0&amp;ui_show_idle_anim:A</t>
@@ -7057,7 +6790,6 @@
           <t>少女战争幻化药(GirlWars 82003 Painting_82003_SkeletonData)</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr">
         <is>
           <t>1</t>
@@ -7085,13 +6817,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H138" t="n">
         <v>0</v>
       </c>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_82004_SkeletonData&amp;ui_show_data:0.8398;0,0&amp;ui_show_idle_anim:A</t>
@@ -7105,7 +6836,6 @@
           <t>少女战争幻化药(GirlWars 82004 Painting_82004_SkeletonData)</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
           <t>1</t>
@@ -7133,13 +6863,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_82005_SkeletonData&amp;ui_show_data:1.1114;0,0&amp;ui_show_idle_anim:A</t>
@@ -7153,7 +6882,6 @@
           <t>少女战争幻化药(GirlWars 82005 Painting_82005_SkeletonData)</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
           <t>1</t>
@@ -7181,13 +6909,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H140" t="n">
         <v>0</v>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_82006_SkeletonData&amp;ui_show_data:0.9656;0,0&amp;ui_show_idle_anim:A</t>
@@ -7201,7 +6928,6 @@
           <t>少女战争幻化药(GirlWars 82006 Painting_82006_SkeletonData)</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
           <t>1</t>
@@ -7229,13 +6955,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H141" t="n">
         <v>0</v>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_82008_SkeletonData&amp;ui_show_data:0.8197;0,0&amp;ui_show_idle_anim:A</t>
@@ -7249,7 +6974,6 @@
           <t>少女战争幻化药(GirlWars 82008 Painting_82008_SkeletonData)</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
           <t>1</t>
@@ -7277,13 +7001,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H142" t="n">
         <v>0</v>
       </c>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_82009_SkeletonData&amp;ui_show_data:1.0981;0,0&amp;ui_show_idle_anim:A</t>
@@ -7297,7 +7020,6 @@
           <t>少女战争幻化药(GirlWars 82009 Painting_82009_SkeletonData)</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
           <t>1</t>
@@ -7325,13 +7047,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H143" t="n">
         <v>0</v>
       </c>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_82010_SkeletonData&amp;ui_show_data:0.6384;0,0&amp;ui_show_idle_anim:A</t>
@@ -7345,7 +7066,6 @@
           <t>少女战争幻化药(GirlWars 82010 Painting_82010_SkeletonData)</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
           <t>1</t>
@@ -7373,13 +7093,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_82011_SkeletonData&amp;ui_show_data:0.4753;0,0&amp;ui_show_idle_anim:A</t>
@@ -7393,7 +7112,6 @@
           <t>少女战争幻化药(GirlWars 82011 Painting_82011_SkeletonData)</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
           <t>1</t>
@@ -7421,13 +7139,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_82012_SkeletonData&amp;ui_show_data:1.1722;0,0&amp;ui_show_idle_anim:A</t>
@@ -7441,7 +7158,6 @@
           <t>少女战争幻化药(GirlWars 82012 Painting_82012_SkeletonData)</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
           <t>1</t>
@@ -7469,13 +7185,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_91001_SkeletonData&amp;ui_show_data:0.6694;0,0&amp;ui_show_idle_anim:A</t>
@@ -7489,7 +7204,6 @@
           <t>少女战争幻化药(GirlWars 91001 Painting_91001_SkeletonData)</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
           <t>1</t>
@@ -7517,13 +7231,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H147" t="n">
         <v>0</v>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_91002_SkeletonData&amp;ui_show_data:0.666;0,0&amp;ui_show_idle_anim:A</t>
@@ -7537,7 +7250,6 @@
           <t>少女战争幻化药(GirlWars 91002 Painting_91002_SkeletonData)</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
           <t>1</t>
@@ -7565,13 +7277,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H148" t="n">
         <v>0</v>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_92001_SkeletonData&amp;ui_show_data:0.3717;0,0&amp;ui_show_idle_anim:A</t>
@@ -7585,7 +7296,6 @@
           <t>少女战争幻化药(GirlWars 92001 Painting_92001_SkeletonData)</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
           <t>1</t>
@@ -7613,13 +7323,12 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H149" t="n">
         <v>0</v>
       </c>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_92002_SkeletonData&amp;ui_show_data:0.7065;0,0&amp;ui_show_idle_anim:A</t>
@@ -7633,7 +7342,6 @@
           <t>少女战争幻化药(GirlWars 92002 Painting_92002_SkeletonData)</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
           <t>1</t>
@@ -7661,13 +7369,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H150" t="n">
         <v>0</v>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_92003_SkeletonData&amp;ui_show_data:0.2735;0,0&amp;ui_show_idle_anim:A</t>
@@ -7681,7 +7388,6 @@
           <t>少女战争幻化药(GirlWars 92003 Painting_92003_SkeletonData)</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
           <t>1</t>
@@ -7709,13 +7415,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H151" t="n">
         <v>0</v>
       </c>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_92004_SkeletonData&amp;ui_show_data:0.4289;0,0&amp;ui_show_idle_anim:A</t>
@@ -7729,7 +7434,6 @@
           <t>少女战争幻化药(GirlWars 92004 Painting_92004_SkeletonData)</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
           <t>1</t>
@@ -7757,13 +7461,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H152" t="n">
         <v>0</v>
       </c>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>ui_show_res:Painting_92005_SkeletonData&amp;ui_show_data:0.6265;0,0&amp;ui_show_idle_anim:A</t>
@@ -7777,7 +7480,6 @@
           <t>少女战争幻化药(GirlWars 92005 Painting_92005_SkeletonData)</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
           <t>1</t>
